--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/NEW_JERSEY_2022.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/NEW_JERSEY_2022.xlsx
@@ -445,7 +445,7 @@
         <v>13</v>
       </c>
       <c r="D5">
-        <v>0.0009465559924275521</v>
+        <v>0.000946555992427552</v>
       </c>
     </row>
     <row r="6">
@@ -1039,7 +1039,7 @@
         <v>13</v>
       </c>
       <c r="D38">
-        <v>0.0009465559924275521</v>
+        <v>0.000946555992427552</v>
       </c>
     </row>
     <row r="39">
@@ -3037,7 +3037,7 @@
         <v>13</v>
       </c>
       <c r="D149">
-        <v>0.0009465559924275521</v>
+        <v>0.000946555992427552</v>
       </c>
     </row>
     <row r="150">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C206">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C215">
@@ -4675,7 +4675,7 @@
         <v>13</v>
       </c>
       <c r="D240">
-        <v>0.0009465559924275521</v>
+        <v>0.000946555992427552</v>
       </c>
     </row>
     <row r="241">
@@ -4801,7 +4801,7 @@
         <v>13</v>
       </c>
       <c r="D247">
-        <v>0.0009465559924275521</v>
+        <v>0.000946555992427552</v>
       </c>
     </row>
     <row r="248">
@@ -5665,7 +5665,7 @@
         <v>126</v>
       </c>
       <c r="D295">
-        <v>0.009174311926605505</v>
+        <v>0.009174311926605503</v>
       </c>
     </row>
     <row r="296">
@@ -7735,7 +7735,7 @@
         <v>13</v>
       </c>
       <c r="D410">
-        <v>0.0009465559924275521</v>
+        <v>0.000946555992427552</v>
       </c>
     </row>
     <row r="411">
@@ -7807,7 +7807,7 @@
         <v>13</v>
       </c>
       <c r="D414">
-        <v>0.0009465559924275521</v>
+        <v>0.000946555992427552</v>
       </c>
     </row>
     <row r="415">
@@ -9409,7 +9409,7 @@
         <v>13</v>
       </c>
       <c r="D503">
-        <v>0.0009465559924275521</v>
+        <v>0.000946555992427552</v>
       </c>
     </row>
     <row r="504">
@@ -9589,7 +9589,7 @@
         <v>135</v>
       </c>
       <c r="D513">
-        <v>0.009829619921363041</v>
+        <v>0.009829619921363039</v>
       </c>
     </row>
     <row r="514">
@@ -10633,7 +10633,7 @@
         <v>13</v>
       </c>
       <c r="D571">
-        <v>0.0009465559924275521</v>
+        <v>0.000946555992427552</v>
       </c>
     </row>
     <row r="572">
@@ -11292,7 +11292,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C608">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C662">
@@ -13369,7 +13369,7 @@
         <v>13</v>
       </c>
       <c r="D723">
-        <v>0.0009465559924275521</v>
+        <v>0.000946555992427552</v>
       </c>
     </row>
     <row r="724">
@@ -15061,7 +15061,7 @@
         <v>13</v>
       </c>
       <c r="D817">
-        <v>0.0009465559924275521</v>
+        <v>0.000946555992427552</v>
       </c>
     </row>
     <row r="818">
@@ -16699,7 +16699,7 @@
         <v>13</v>
       </c>
       <c r="D908">
-        <v>0.0009465559924275521</v>
+        <v>0.000946555992427552</v>
       </c>
     </row>
     <row r="909">
@@ -16717,7 +16717,7 @@
         <v>131</v>
       </c>
       <c r="D909">
-        <v>0.009538371923693025</v>
+        <v>0.009538371923693023</v>
       </c>
     </row>
     <row r="910">
@@ -17599,7 +17599,7 @@
         <v>13</v>
       </c>
       <c r="D958">
-        <v>0.0009465559924275521</v>
+        <v>0.000946555992427552</v>
       </c>
     </row>
     <row r="959">
@@ -19435,7 +19435,7 @@
         <v>13</v>
       </c>
       <c r="D1060">
-        <v>0.0009465559924275521</v>
+        <v>0.000946555992427552</v>
       </c>
     </row>
     <row r="1061">
@@ -19633,7 +19633,7 @@
         <v>13</v>
       </c>
       <c r="D1071">
-        <v>0.0009465559924275521</v>
+        <v>0.000946555992427552</v>
       </c>
     </row>
     <row r="1072">
@@ -20317,7 +20317,7 @@
         <v>13</v>
       </c>
       <c r="D1109">
-        <v>0.0009465559924275521</v>
+        <v>0.000946555992427552</v>
       </c>
     </row>
     <row r="1110">
@@ -21289,7 +21289,7 @@
         <v>13</v>
       </c>
       <c r="D1163">
-        <v>0.0009465559924275521</v>
+        <v>0.000946555992427552</v>
       </c>
     </row>
     <row r="1164">
